--- a/multi seed generators/merged 10 seeds/regression/results/aggregated/compute_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/regression/results/aggregated/compute_mean_sd.xlsx
@@ -333,12 +333,10 @@
       <c r="O3" t="n">
         <v>0.0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P3"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -617,12 +615,10 @@
       <c r="O7" t="n">
         <v>0.0</v>
       </c>
-      <c r="P7" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P7"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -901,12 +897,10 @@
       <c r="O11" t="n">
         <v>0.0</v>
       </c>
-      <c r="P11" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P11"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1185,12 +1179,10 @@
       <c r="O15" t="n">
         <v>0.0</v>
       </c>
-      <c r="P15" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P15"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -1469,12 +1461,10 @@
       <c r="O19" t="n">
         <v>0.0</v>
       </c>
-      <c r="P19" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P19"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -1753,12 +1743,10 @@
       <c r="O23" t="n">
         <v>0.0</v>
       </c>
-      <c r="P23" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P23"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -2037,12 +2025,10 @@
       <c r="O27" t="n">
         <v>0.0</v>
       </c>
-      <c r="P27" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P27"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -2321,12 +2307,10 @@
       <c r="O31" t="n">
         <v>0.0</v>
       </c>
-      <c r="P31" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P31"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -2605,12 +2589,10 @@
       <c r="O35" t="n">
         <v>0.0</v>
       </c>
-      <c r="P35" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P35"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -2889,12 +2871,10 @@
       <c r="O39" t="n">
         <v>0.0</v>
       </c>
-      <c r="P39" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P39"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3173,12 +3153,10 @@
       <c r="O43" t="n">
         <v>0.0</v>
       </c>
-      <c r="P43" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P43"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -3457,12 +3435,10 @@
       <c r="O47" t="n">
         <v>0.0</v>
       </c>
-      <c r="P47" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P47"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -3741,12 +3717,10 @@
       <c r="O51" t="n">
         <v>0.0</v>
       </c>
-      <c r="P51" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P51"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -4025,12 +3999,10 @@
       <c r="O55" t="n">
         <v>0.0</v>
       </c>
-      <c r="P55" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P55"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R55" t="n">
@@ -4309,12 +4281,10 @@
       <c r="O59" t="n">
         <v>0.0</v>
       </c>
-      <c r="P59" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P59"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R59" t="n">
@@ -4593,12 +4563,10 @@
       <c r="O63" t="n">
         <v>0.0</v>
       </c>
-      <c r="P63" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P63"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -4877,12 +4845,10 @@
       <c r="O67" t="n">
         <v>0.0</v>
       </c>
-      <c r="P67" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P67"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -5161,12 +5127,10 @@
       <c r="O71" t="n">
         <v>0.0</v>
       </c>
-      <c r="P71" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P71"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -5445,12 +5409,10 @@
       <c r="O75" t="n">
         <v>0.0</v>
       </c>
-      <c r="P75" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P75"/>
       <c r="Q75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -5729,12 +5691,10 @@
       <c r="O79" t="n">
         <v>0.0</v>
       </c>
-      <c r="P79" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P79"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -6013,12 +5973,10 @@
       <c r="O83" t="n">
         <v>0.0</v>
       </c>
-      <c r="P83" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P83"/>
       <c r="Q83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R83" t="n">
@@ -6297,12 +6255,10 @@
       <c r="O87" t="n">
         <v>0.0</v>
       </c>
-      <c r="P87" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P87"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -6581,12 +6537,10 @@
       <c r="O91" t="n">
         <v>0.0</v>
       </c>
-      <c r="P91" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P91"/>
       <c r="Q91" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R91" t="n">
@@ -6865,12 +6819,10 @@
       <c r="O95" t="n">
         <v>0.0</v>
       </c>
-      <c r="P95" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P95"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R95" t="n">
@@ -7149,12 +7101,10 @@
       <c r="O99" t="n">
         <v>0.0</v>
       </c>
-      <c r="P99" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P99"/>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -7433,12 +7383,10 @@
       <c r="O103" t="n">
         <v>0.0</v>
       </c>
-      <c r="P103" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P103"/>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -7717,12 +7665,10 @@
       <c r="O107" t="n">
         <v>0.0</v>
       </c>
-      <c r="P107" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P107"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R107" t="n">
@@ -8001,12 +7947,10 @@
       <c r="O111" t="n">
         <v>0.0</v>
       </c>
-      <c r="P111" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P111"/>
       <c r="Q111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -8285,12 +8229,10 @@
       <c r="O115" t="n">
         <v>0.0</v>
       </c>
-      <c r="P115" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P115"/>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R115" t="n">
@@ -8569,12 +8511,10 @@
       <c r="O119" t="n">
         <v>0.0</v>
       </c>
-      <c r="P119" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P119"/>
       <c r="Q119" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R119" t="n">
@@ -8853,12 +8793,10 @@
       <c r="O123" t="n">
         <v>0.0</v>
       </c>
-      <c r="P123" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P123"/>
       <c r="Q123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -9137,12 +9075,10 @@
       <c r="O127" t="n">
         <v>0.0</v>
       </c>
-      <c r="P127" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P127"/>
       <c r="Q127" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R127" t="n">
@@ -9421,12 +9357,10 @@
       <c r="O131" t="n">
         <v>0.0</v>
       </c>
-      <c r="P131" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P131"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R131" t="n">
@@ -9705,12 +9639,10 @@
       <c r="O135" t="n">
         <v>0.0</v>
       </c>
-      <c r="P135" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P135"/>
       <c r="Q135" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -9989,12 +9921,10 @@
       <c r="O139" t="n">
         <v>0.0</v>
       </c>
-      <c r="P139" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P139"/>
       <c r="Q139" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R139" t="n">
@@ -10273,12 +10203,10 @@
       <c r="O143" t="n">
         <v>0.0</v>
       </c>
-      <c r="P143" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P143"/>
       <c r="Q143" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -10557,12 +10485,10 @@
       <c r="O147" t="n">
         <v>0.0</v>
       </c>
-      <c r="P147" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P147"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R147" t="n">
@@ -10841,12 +10767,10 @@
       <c r="O151" t="n">
         <v>0.0</v>
       </c>
-      <c r="P151" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P151"/>
       <c r="Q151" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R151" t="n">
@@ -11125,12 +11049,10 @@
       <c r="O155" t="n">
         <v>0.0</v>
       </c>
-      <c r="P155" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P155"/>
       <c r="Q155" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R155" t="n">
@@ -11409,12 +11331,10 @@
       <c r="O159" t="n">
         <v>0.0</v>
       </c>
-      <c r="P159" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P159"/>
       <c r="Q159" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R159" t="n">
@@ -11693,12 +11613,10 @@
       <c r="O163" t="n">
         <v>0.0</v>
       </c>
-      <c r="P163" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P163"/>
       <c r="Q163" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R163" t="n">
@@ -11977,12 +11895,10 @@
       <c r="O167" t="n">
         <v>0.0</v>
       </c>
-      <c r="P167" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P167"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R167" t="n">
@@ -12261,12 +12177,10 @@
       <c r="O171" t="n">
         <v>0.0</v>
       </c>
-      <c r="P171" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P171"/>
       <c r="Q171" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R171" t="n">
@@ -12545,12 +12459,10 @@
       <c r="O175" t="n">
         <v>0.0</v>
       </c>
-      <c r="P175" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P175"/>
       <c r="Q175" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R175" t="n">
@@ -12829,12 +12741,10 @@
       <c r="O179" t="n">
         <v>0.0</v>
       </c>
-      <c r="P179" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P179"/>
       <c r="Q179" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R179" t="n">
@@ -13113,12 +13023,10 @@
       <c r="O183" t="n">
         <v>0.0</v>
       </c>
-      <c r="P183" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P183"/>
       <c r="Q183" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R183" t="n">
@@ -13397,12 +13305,10 @@
       <c r="O187" t="n">
         <v>0.0</v>
       </c>
-      <c r="P187" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P187"/>
       <c r="Q187" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R187" t="n">
@@ -13681,12 +13587,10 @@
       <c r="O191" t="n">
         <v>0.0</v>
       </c>
-      <c r="P191" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P191"/>
       <c r="Q191" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 ± 0</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="R191" t="n">
